--- a/artfynd/A 32277-2021 artfynd.xlsx
+++ b/artfynd/A 32277-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 32277-2021 artfynd.xlsx
+++ b/artfynd/A 32277-2021 artfynd.xlsx
@@ -1884,7 +1884,7 @@
         <v>117978126</v>
       </c>
       <c r="B11" t="n">
-        <v>77821</v>
+        <v>77823</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>

--- a/artfynd/A 32277-2021 artfynd.xlsx
+++ b/artfynd/A 32277-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY11"/>
+  <dimension ref="A1:AY13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>17225406</v>
       </c>
       <c r="B2" t="n">
-        <v>89338</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91859</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>461981.5127676898</v>
+        <v>461982</v>
       </c>
       <c r="R2" t="n">
-        <v>7173933.224629633</v>
+        <v>7173933</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,19 +743,9 @@
           <t>2014-07-03</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-07-03</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -809,50 +794,45 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17225404</v>
+        <v>117978126</v>
       </c>
       <c r="B3" t="n">
-        <v>89388</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>78686</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1108</v>
+        <v>498</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Harticka</t>
+          <t>Liten sotlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Pelloporus leporinus</t>
+          <t>Acolium karelicum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Krieglst.</t>
+          <t>(Vain.) M.Prieto &amp; Wedin</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>N Väktarklumpen, mellan Storflon och kraftverksdammen S om Hovden, Jmt</t>
+          <t>Säterbäcken, Säterbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>461997.6913642348</v>
+        <v>462226</v>
       </c>
       <c r="R3" t="n">
-        <v>7174163.310157894</v>
+        <v>7174159</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -879,22 +859,12 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2024-06-23</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -905,75 +875,48 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AN3" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>1 substratenheter # Picea abies</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
+          <t>Joel Schill</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Magnus Johansson</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>SCA Skog Naturvärdesinventering</t>
-        </is>
-      </c>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>17225409</v>
+        <v>17225404</v>
       </c>
       <c r="B4" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91905</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1249</v>
+        <v>1108</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Norsk näverlav</t>
+          <t>Harticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Platismatia norvegica</t>
+          <t>Pelloporus leporinus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+          <t>(Fr.) Krieglst.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -983,10 +926,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>462275.0672090334</v>
+        <v>461998</v>
       </c>
       <c r="R4" t="n">
-        <v>7174205.634888814</v>
+        <v>7174163</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1013,22 +956,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2014-07-04</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2014-07-04</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1080,16 +1013,11 @@
         <v>17225405</v>
       </c>
       <c r="B5" t="n">
-        <v>89406</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91923</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1117,10 +1045,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>461989.6801129328</v>
+        <v>461990</v>
       </c>
       <c r="R5" t="n">
-        <v>7174003.323392701</v>
+        <v>7174003</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1150,19 +1078,9 @@
           <t>2014-07-03</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2014-07-03</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1211,15 +1129,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>17225411</v>
+        <v>17225389</v>
       </c>
       <c r="B6" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1251,10 +1164,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>462096.7491539326</v>
+        <v>462324</v>
       </c>
       <c r="R6" t="n">
-        <v>7174236.542838341</v>
+        <v>7174437</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1281,22 +1194,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2014-07-04</t>
-        </is>
-      </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2014-07-04</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1345,15 +1248,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>17225398</v>
+        <v>17225397</v>
       </c>
       <c r="B7" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1385,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>461986.9993087233</v>
+        <v>462004</v>
       </c>
       <c r="R7" t="n">
-        <v>7174233.212687199</v>
+        <v>7173853</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1418,19 +1316,9 @@
           <t>2014-07-03</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2014-07-03</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1479,15 +1367,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>17225407</v>
+        <v>17225398</v>
       </c>
       <c r="B8" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1519,10 +1402,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>462255.5997367481</v>
+        <v>461987</v>
       </c>
       <c r="R8" t="n">
-        <v>7174328.290010757</v>
+        <v>7174233</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1549,22 +1432,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2014-07-04</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2014-07-04</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-07-03</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1613,15 +1486,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>17225397</v>
+        <v>17225407</v>
       </c>
       <c r="B9" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1653,10 +1521,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>462003.6525194288</v>
+        <v>462256</v>
       </c>
       <c r="R9" t="n">
-        <v>7173853.325621127</v>
+        <v>7174328</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1683,22 +1551,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-07-04</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2014-07-03</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2014-07-04</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1747,15 +1605,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>17225410</v>
+        <v>17225408</v>
       </c>
       <c r="B10" t="n">
-        <v>77668</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1787,10 +1640,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>462277.5806413802</v>
+        <v>462316</v>
       </c>
       <c r="R10" t="n">
-        <v>7174166.653180626</v>
+        <v>7174306</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1820,19 +1673,9 @@
           <t>2014-07-04</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2014-07-04</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1881,15 +1724,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>117978126</v>
+        <v>17225409</v>
       </c>
       <c r="B11" t="n">
-        <v>77825</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79486</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1897,34 +1735,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>498</v>
+        <v>1249</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Liten sotlav</t>
+          <t>Norsk näverlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Acolium karelicum</t>
+          <t>Platismatia norvegica</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Vain.) M.Prieto &amp; Wedin</t>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Säterbäcken (Säterbäcken), Jmt</t>
+          <t>N Väktarklumpen, mellan Storflon och kraftverksdammen S om Hovden, Jmt</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>462226</v>
+        <v>462275</v>
       </c>
       <c r="R11" t="n">
-        <v>7174159</v>
+        <v>7174206</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1951,12 +1789,12 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2014-07-04</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2024-06-23</t>
+          <t>2014-07-04</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1967,19 +1805,279 @@
       </c>
       <c r="AG11" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ11" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK11" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN11" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO11" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
       </c>
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
+          <t>Magnus Johansson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Joel Schill</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>17225410</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79486</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>N Väktarklumpen, mellan Storflon och kraftverksdammen S om Hovden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>462278</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7174167</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2014-07-04</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2014-07-04</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ12" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK12" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN12" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO12" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>17225411</v>
+      </c>
+      <c r="B13" t="n">
+        <v>79486</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>N Väktarklumpen, mellan Storflon och kraftverksdammen S om Hovden, Jmt</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>462097</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7174237</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2014-07-04</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2014-07-04</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AN13" t="n">
+        <v>1</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>1 substratenheter # Picea abies</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Magnus Johansson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>SCA Skog Naturvärdesinventering</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 32277-2021 artfynd.xlsx
+++ b/artfynd/A 32277-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY13"/>
+  <dimension ref="A1:AY14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2079,6 +2079,103 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>134519679</v>
+      </c>
+      <c r="B14" t="n">
+        <v>79532</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>1249</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Norsk näverlav</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Platismatia norvegica</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Lynge) W.L.Culb. &amp; C.F.Culb.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Storflon, Storflon, Jmt</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>461958</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7173842</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Strömsund</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Frostviken</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2026-06-20</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Joel Schill</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
